--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_magallanes_y_la_antartica_chilena.xlsx
@@ -413,7 +413,7 @@
         <v>11.86440677966102</v>
       </c>
       <c r="D3">
-        <v>58.19209039548023</v>
+        <v>58.19209039548022</v>
       </c>
       <c r="E3">
         <v>29.94350282485876</v>
@@ -454,7 +454,7 @@
         <v>61.37339055793991</v>
       </c>
       <c r="E5">
-        <v>23.60515021459227</v>
+        <v>23.60515021459228</v>
       </c>
     </row>
     <row r="6">
@@ -508,10 +508,10 @@
         <v>20.53742802303263</v>
       </c>
       <c r="D8">
-        <v>57.38963531669866</v>
+        <v>57.38963531669867</v>
       </c>
       <c r="E8">
-        <v>22.07293666026871</v>
+        <v>22.07293666026872</v>
       </c>
     </row>
     <row r="9">
@@ -527,7 +527,7 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>63.42857142857143</v>
+        <v>63.42857142857144</v>
       </c>
       <c r="E9">
         <v>16.57142857142857</v>
@@ -562,7 +562,7 @@
         <v>129.4117647058823</v>
       </c>
       <c r="C11">
-        <v>8.629441624365482</v>
+        <v>8.629441624365484</v>
       </c>
       <c r="D11">
         <v>80.20304568527919</v>
